--- a/DuePrint3 BOM.xlsx
+++ b/DuePrint3 BOM.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jared\Documents\GitHub\DuePrint3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A541FB-66A6-43F4-A855-6E999223EA04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A7C2F95-A385-47A1-A6DD-365DEDA3304F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{EE4BCC0D-CA0F-44AB-9A6C-651FC0043629}"/>
+    <workbookView xWindow="11520" yWindow="1860" windowWidth="35895" windowHeight="17805" xr2:uid="{EE4BCC0D-CA0F-44AB-9A6C-651FC0043629}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$I$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$I$67</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="159">
   <si>
     <t>Item</t>
   </si>
@@ -83,72 +83,18 @@
     <t>SAMMY-C21 Module</t>
   </si>
   <si>
-    <t>NUCLEO-L476RG</t>
-  </si>
-  <si>
-    <t>Need USB Mini B cable for programming</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/dp/B01IO3N646</t>
-  </si>
-  <si>
-    <t>STM32 Nucleo-64, L476RG</t>
-  </si>
-  <si>
-    <t>DuePrint3 v1.0.0 PCB</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/molex/0430452412/531416</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/molex/0430451812/531413</t>
-  </si>
-  <si>
-    <t>EHT-120-01-S-D</t>
-  </si>
-  <si>
-    <t>Conn, Header, 40 pos, EHT</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/samtec-inc/EHT-120-01-S-D/1106698</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/samtec-inc/EHT-110-01-S-D/1106695</t>
-  </si>
-  <si>
     <t>Conn, Header, 20 pos, EHT</t>
   </si>
   <si>
-    <t>EHT-110-01-S-D</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/sullins-connector-solutions/PPPC161LFBN-RC/810188</t>
-  </si>
-  <si>
-    <t>PPPC161LFBN-RC</t>
-  </si>
-  <si>
     <t>Conn, Header, 16 pos</t>
   </si>
   <si>
-    <t>54601-906002WPLF</t>
-  </si>
-  <si>
     <t>Conn, 6p4c R/A</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/amphenol-cs-fci/54601-906002WPLF/4242890</t>
-  </si>
-  <si>
     <t>https://www.digikey.com/en/products/detail/molex/0436500215/283461</t>
   </si>
   <si>
-    <t>Conn, Header, 24 pos, Micro-Fit  3.0</t>
-  </si>
-  <si>
-    <t>Conn, Header, 18 pos, Micro-Fit  3.0</t>
-  </si>
-  <si>
     <t>Conn, Header, 2 pos, MicroFit- 3.0</t>
   </si>
   <si>
@@ -173,69 +119,15 @@
     <t>https://www.digikey.com/en/products/detail/harwin-inc/M20-9990345/3728227</t>
   </si>
   <si>
-    <t>Conn, Header, 8 pos, Micro-Fit 3.0</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/molex/0436500815/531388</t>
-  </si>
-  <si>
-    <t>J2,J3</t>
-  </si>
-  <si>
-    <t>J4,J5</t>
-  </si>
-  <si>
-    <t>J7,J10</t>
-  </si>
-  <si>
-    <t>J11,J12</t>
-  </si>
-  <si>
     <t>J6</t>
   </si>
   <si>
-    <t>J8</t>
-  </si>
-  <si>
     <t>J14</t>
   </si>
   <si>
-    <t>J13,J15</t>
-  </si>
-  <si>
     <t>J1</t>
   </si>
   <si>
-    <t>J9</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>R7,R9,R11,R13,R15,R18</t>
-  </si>
-  <si>
-    <t>R8,R10,R12,R14,R16,R19</t>
-  </si>
-  <si>
-    <t>R20,R21,R22,R23,R24,R25</t>
-  </si>
-  <si>
-    <t>R1,R3,R4</t>
-  </si>
-  <si>
-    <t>R2,R5,R6</t>
-  </si>
-  <si>
-    <t>R17</t>
-  </si>
-  <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
     <t>0.1 uF Cap, 0805</t>
   </si>
   <si>
@@ -275,12 +167,6 @@
     <t>https://www.digikey.com/en/products/detail/vishay-dale/CRCW08051K00FKEA/1175637</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/vishay-general-semiconductor-diodes-division/SS1FH10-M3-H/6012246</t>
-  </si>
-  <si>
-    <t>Schottky Diode, 100V 1A, DO-219AB</t>
-  </si>
-  <si>
     <t>SN74AHCT125DR, 14-SOIC</t>
   </si>
   <si>
@@ -308,87 +194,33 @@
     <t>CRCW08051K00FKEA</t>
   </si>
   <si>
-    <t>SS1FH10-M3/H</t>
-  </si>
-  <si>
     <t>Conn, Plug, 8 pos, Mini-Fit Jr</t>
   </si>
   <si>
     <t>https://www.digikey.com/en/products/detail/molex/0039012086/930285</t>
   </si>
   <si>
-    <t>P2</t>
-  </si>
-  <si>
     <t>Conn, Rcpt, 20 pos, Mini-Fit Jr</t>
   </si>
   <si>
-    <t>P3</t>
-  </si>
-  <si>
     <t>https://www.digikey.com/en/products/detail/molex/0039012205/930279</t>
   </si>
   <si>
     <t>Conn, Plug, 20 pos, Mini-Fit Jr</t>
   </si>
   <si>
-    <t>P1</t>
-  </si>
-  <si>
     <t>https://www.digikey.com/en/products/detail/molex/0039012206/4693014</t>
   </si>
   <si>
-    <t>Pin, 18-24 AWG, Mini-Fit Jr</t>
-  </si>
-  <si>
-    <t>Don't use these, as they're designed for very large jackets. Recommend 39000049 instead</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/molex/0039000041/61445</t>
-  </si>
-  <si>
-    <t>Socket, 18-24 AWG, Mini-Fit Jr</t>
-  </si>
-  <si>
-    <t>Don't use these, as they're designed for very large jackets. Recommend 39000047 instead</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/molex/0039000039/61448</t>
-  </si>
-  <si>
     <t>https://www.digikey.com/en/products/detail/molex/0430300007/252479</t>
   </si>
   <si>
     <t>Socket, 20-24 AWG, Micro-Fit 3.0</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/molex/0430252400/531410</t>
-  </si>
-  <si>
-    <t>P8</t>
-  </si>
-  <si>
-    <t>Conn, Rcpt, 24 pos, Micro-Fit 3.0</t>
-  </si>
-  <si>
-    <t>P9</t>
-  </si>
-  <si>
-    <t>Conn, Rcpt, 18 pos, Micro-Fit 3.0</t>
-  </si>
-  <si>
-    <t>Conn, Rcpt, 8 pos, Micro-Fit 3.0</t>
-  </si>
-  <si>
     <t>https://www.digikey.com/en/products/detail/molex/0430251800/531407</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/molex/0436450800/531322</t>
-  </si>
-  <si>
-    <t>P10</t>
-  </si>
-  <si>
     <t>P4,P5,P6</t>
   </si>
   <si>
@@ -449,27 +281,6 @@
     <t>Socket, 22-28 AWG, WR-WTB</t>
   </si>
   <si>
-    <t>https://www.filastruder.com/collections/duet3d/products/duet-can-fd-cable?variant=39510523281479</t>
-  </si>
-  <si>
-    <t>CAN-FD Cable, 1m</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/dp/B01EV70C78</t>
-  </si>
-  <si>
-    <t>120pcs 200mm Dupont Jumpers</t>
-  </si>
-  <si>
-    <t>22 AWG Wire</t>
-  </si>
-  <si>
-    <t>https://www.remingtonindustries.com/hook-up-wire/hook-up-wire-22-awg-stranded-solid-kit-2-color-sets-2-spool-sizes-available/</t>
-  </si>
-  <si>
-    <t>As required/desired. Smaller gauges likely would be acceptable for most connections excluding motor wires</t>
-  </si>
-  <si>
     <t>RJ11 connectors</t>
   </si>
   <si>
@@ -485,12 +296,6 @@
     <t>https://www.digikey.com/en/products/detail/sullins-connector-solutions/QPC02SXGN-RC/2618262</t>
   </si>
   <si>
-    <t>For CAN-FD termination, or later filament detector connection</t>
-  </si>
-  <si>
-    <t>As required</t>
-  </si>
-  <si>
     <t>Likely need to source 16pin headers</t>
   </si>
   <si>
@@ -504,6 +309,216 @@
   </si>
   <si>
     <t>AC is spliced in from the printer's power inlet, meaning right now the Duet's power cannot be controlled from front on/off switch (though front on/off switch functionality is also not fully present on PCB)</t>
+  </si>
+  <si>
+    <t>Pin, 22-28 AWG, Mini-Fit Jr</t>
+  </si>
+  <si>
+    <t>Socket, 22-28 AWG, Mini-Fit Jr</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/molex/0039000048/1643437</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/molex/0039000046/1643436</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/samtec-inc/EHT-110-01-F-D/6678014</t>
+  </si>
+  <si>
+    <t>EHT-110-01-F-D</t>
+  </si>
+  <si>
+    <t>DFR0864</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/dfrobot/DFR0864/14824968</t>
+  </si>
+  <si>
+    <t>USB C for programming</t>
+  </si>
+  <si>
+    <t>STM32F411 BLACKPILL</t>
+  </si>
+  <si>
+    <t>DuePrint3 v2.0.0 PCB</t>
+  </si>
+  <si>
+    <t>EHT-125-01-S-D</t>
+  </si>
+  <si>
+    <t>Conn, Header, 50 pos, EHT</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/samtec-inc/EHT-125-01-S-D/1106701</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/w%C3%BCrth-elektronik/61301611821/6137797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	
+SS-6466S-A-PG1</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/stewart-connector/SS-6466S-A-PG1/1642347</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/w%C3%BCrth-elektronik/61302011821/16608603</t>
+  </si>
+  <si>
+    <t>Conn, Header, 20 pos</t>
+  </si>
+  <si>
+    <t>B30B-PHDSS</t>
+  </si>
+  <si>
+    <t>Conn, Header, 30 pos, JST PHD, 2.0</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/jst-sales-america-inc/B30B-PHDSS/926678</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/jst-sales-america-inc/B14B-PHDSS/926670</t>
+  </si>
+  <si>
+    <t>Conn, Header, 14 pos, JST PHD, 2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	
+B14B-PHDSS</t>
+  </si>
+  <si>
+    <t>PHDR-30VS</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/jst-sales-america-inc/PHDR-30VS/608621</t>
+  </si>
+  <si>
+    <t>Conn, Rcpt, 30 pos, JST PHD, 2.0</t>
+  </si>
+  <si>
+    <t>Conn, Rcpt, 14 pos, JST PHD, 2.0</t>
+  </si>
+  <si>
+    <t>PHDR-14VS</t>
+  </si>
+  <si>
+    <t>ERJ-6ENF1003V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	
+RES SMD 100K OHM 1% 1/8W 0805</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/panasonic-electronic-components/ERJ-6ENF1003V/111841</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/samsung-electro-mechanics/CL21B103KAANNNC/3888092</t>
+  </si>
+  <si>
+    <t>CL21B103KAANNNC</t>
+  </si>
+  <si>
+    <t>CAP CER 10000PF 25V X7R 0805</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/350720-1/213757</t>
+  </si>
+  <si>
+    <t>350720-1</t>
+  </si>
+  <si>
+    <t>350782-1</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/350782-1/213758</t>
+  </si>
+  <si>
+    <t>350561-1</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/350561-1/287669</t>
+  </si>
+  <si>
+    <t>350218-1</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/350218-1/287751</t>
+  </si>
+  <si>
+    <t>350536-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	350570-1</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/350570-1/287662</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/350536-1/287712</t>
+  </si>
+  <si>
+    <t>U4</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>J16</t>
+  </si>
+  <si>
+    <t>J2, J5</t>
+  </si>
+  <si>
+    <t>J11, J12</t>
+  </si>
+  <si>
+    <t>J3. J4. J8</t>
+  </si>
+  <si>
+    <t>J13</t>
+  </si>
+  <si>
+    <t>C1, C2</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>R10, R11, R12, R13, R14, R15, R17</t>
+  </si>
+  <si>
+    <t>R3, R4, R6</t>
+  </si>
+  <si>
+    <t>R5, R7, R8</t>
+  </si>
+  <si>
+    <t>R16</t>
+  </si>
+  <si>
+    <t>U1, U2</t>
+  </si>
+  <si>
+    <t>14AWG</t>
+  </si>
+  <si>
+    <t>18AWG</t>
+  </si>
+  <si>
+    <t>28AWG</t>
+  </si>
+  <si>
+    <t>22AWG</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/molex/0039012040/61376</t>
+  </si>
+  <si>
+    <t>For CAN-FD termination</t>
   </si>
 </sst>
 </file>
@@ -553,7 +568,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -563,6 +578,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -596,7 +617,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -639,6 +660,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -977,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5704B641-D666-4847-A317-F8C12FBC4158}">
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="5" bestFit="1" customWidth="1"/>
@@ -987,7 +1017,7 @@
     <col min="5" max="5" width="34.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.5703125" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="40.5703125" style="3" customWidth="1"/>
     <col min="9" max="9" width="120.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -995,7 +1025,7 @@
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F1" s="7">
         <f>SUM(G:G)</f>
-        <v>471.0900000000002</v>
+        <v>452.43224266666704</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1064,16 +1094,18 @@
       <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="12"/>
+      <c r="E4" s="12" t="s">
+        <v>138</v>
+      </c>
       <c r="F4" s="13">
         <v>34.99</v>
       </c>
       <c r="G4" s="13">
-        <f t="shared" ref="G4:G42" si="0">D4*F4</f>
+        <f t="shared" ref="G4:G40" si="0">D4*F4</f>
         <v>34.99</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>11</v>
@@ -1084,27 +1116,29 @@
         <v>3</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>17</v>
+        <v>96</v>
+      </c>
+      <c r="C5" t="s">
+        <v>99</v>
       </c>
       <c r="D5" s="12">
         <v>1</v>
       </c>
-      <c r="E5" s="12"/>
+      <c r="E5" s="12" t="s">
+        <v>139</v>
+      </c>
       <c r="F5" s="13">
-        <v>23.99</v>
+        <v>16.5</v>
       </c>
       <c r="G5" s="13">
         <f t="shared" si="0"/>
-        <v>23.99</v>
+        <v>16.5</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>16</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1113,18 +1147,19 @@
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="12" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="D6" s="12">
         <v>1</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="13">
-        <v>40.6</v>
+        <f>70.4/3</f>
+        <v>23.466666666666669</v>
       </c>
       <c r="G6" s="13">
         <f t="shared" si="0"/>
-        <v>40.6</v>
+        <v>23.466666666666669</v>
       </c>
       <c r="H6" s="14"/>
     </row>
@@ -1133,10 +1168,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>151</v>
+        <v>86</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>152</v>
+        <v>87</v>
       </c>
       <c r="D7" s="12">
         <v>1</v>
@@ -1150,94 +1185,94 @@
         <v>15.6</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>154</v>
+        <v>89</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>153</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>6</v>
       </c>
-      <c r="B8" s="12">
-        <v>430452412</v>
+      <c r="B8" s="12" t="s">
+        <v>109</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="D8" s="12">
         <v>1</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>54</v>
+        <v>140</v>
       </c>
       <c r="F8" s="13">
-        <v>3.51</v>
+        <v>0.86</v>
       </c>
       <c r="G8" s="13">
         <f t="shared" si="0"/>
-        <v>3.51</v>
+        <v>0.86</v>
       </c>
       <c r="H8" s="14"/>
       <c r="I8" s="2" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>7</v>
       </c>
-      <c r="B9" s="12">
-        <v>430451812</v>
+      <c r="B9" s="14" t="s">
+        <v>114</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>35</v>
+        <v>113</v>
       </c>
       <c r="D9" s="12">
         <v>1</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="F9" s="13">
-        <v>2.48</v>
+        <v>0.47</v>
       </c>
       <c r="G9" s="13">
         <f t="shared" si="0"/>
-        <v>2.48</v>
+        <v>0.47</v>
       </c>
       <c r="H9" s="14"/>
       <c r="I9" s="2" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>8</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>21</v>
+      <c r="B10" t="s">
+        <v>101</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>22</v>
+        <v>102</v>
       </c>
       <c r="D10" s="12">
         <v>2</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
       <c r="F10" s="13">
-        <v>13.46</v>
+        <v>6.91</v>
       </c>
       <c r="G10" s="13">
         <f t="shared" si="0"/>
-        <v>26.92</v>
+        <v>13.82</v>
       </c>
       <c r="H10" s="14"/>
       <c r="I10" s="2" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1245,83 +1280,81 @@
         <v>9</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D11" s="12">
         <v>1</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="F11" s="13">
-        <v>6.54</v>
+        <v>2.77</v>
       </c>
       <c r="G11" s="13">
         <f t="shared" si="0"/>
-        <v>6.54</v>
+        <v>2.77</v>
       </c>
       <c r="H11" s="14"/>
       <c r="I11" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>10</v>
       </c>
-      <c r="B12" s="12" t="s">
-        <v>28</v>
+      <c r="B12" s="12">
+        <v>61301611821</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D12" s="12">
         <v>2</v>
       </c>
-      <c r="E12" s="12" t="s">
-        <v>46</v>
-      </c>
+      <c r="E12" s="12"/>
       <c r="F12" s="13">
-        <v>0.93</v>
+        <v>0.61</v>
       </c>
       <c r="G12" s="13">
         <f t="shared" si="0"/>
-        <v>1.86</v>
+        <v>1.22</v>
       </c>
       <c r="H12" s="14"/>
       <c r="I12" s="2" t="s">
-        <v>27</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>11</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>30</v>
+      <c r="B13" s="14" t="s">
+        <v>105</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D13" s="12">
         <v>2</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>47</v>
+        <v>142</v>
       </c>
       <c r="F13" s="13">
-        <v>0.2</v>
+        <v>1.78</v>
       </c>
       <c r="G13" s="13">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>3.56</v>
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="2" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1332,24 +1365,24 @@
         <v>436500215</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="D14" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>48</v>
+        <v>143</v>
       </c>
       <c r="F14" s="13">
         <v>0.89</v>
       </c>
       <c r="G14" s="13">
         <f t="shared" si="0"/>
-        <v>1.78</v>
+        <v>2.67</v>
       </c>
       <c r="H14" s="14"/>
       <c r="I14" s="2" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1357,29 +1390,29 @@
         <v>13</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D15" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="F15" s="13">
         <v>0.12</v>
       </c>
       <c r="G15" s="13">
         <f t="shared" si="0"/>
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1387,16 +1420,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D16" s="12">
         <v>1</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>50</v>
+        <v>144</v>
       </c>
       <c r="F16" s="13">
         <v>0.15</v>
@@ -1406,10 +1439,10 @@
         <v>0.15</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1417,27 +1450,25 @@
         <v>15</v>
       </c>
       <c r="B17" s="12">
-        <v>436500815</v>
+        <v>61302011821</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="D17" s="12">
-        <v>1</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>51</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E17" s="12"/>
       <c r="F17" s="13">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="G17" s="13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>1.66</v>
       </c>
       <c r="H17" s="14"/>
       <c r="I17" s="2" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1445,27 +1476,27 @@
         <v>16</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="D18" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="F18" s="13">
+        <v>145</v>
+      </c>
+      <c r="F18" s="16">
         <v>0.1</v>
       </c>
-      <c r="G18" s="13">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
+      <c r="G18" s="16">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="H18" s="14"/>
-      <c r="I18" s="2" t="s">
-        <v>72</v>
+      <c r="I18" s="17" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1473,27 +1504,27 @@
         <v>17</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="D19" s="12">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" s="13">
+        <v>146</v>
+      </c>
+      <c r="F19" s="16">
         <v>0.1</v>
       </c>
-      <c r="G19" s="13">
-        <f t="shared" si="0"/>
-        <v>0.60000000000000009</v>
+      <c r="G19" s="16">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
       </c>
       <c r="H19" s="14"/>
-      <c r="I19" s="2" t="s">
-        <v>73</v>
+      <c r="I19" s="17" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1501,27 +1532,27 @@
         <v>18</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="D20" s="12">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="F20" s="13">
+        <v>147</v>
+      </c>
+      <c r="F20" s="16">
         <v>0.1</v>
       </c>
-      <c r="G20" s="13">
-        <f t="shared" si="0"/>
-        <v>0.60000000000000009</v>
+      <c r="G20" s="16">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
       </c>
       <c r="H20" s="14"/>
-      <c r="I20" s="2" t="s">
-        <v>74</v>
+      <c r="I20" s="17" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1529,27 +1560,27 @@
         <v>19</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="D21" s="12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F21" s="13">
+        <v>148</v>
+      </c>
+      <c r="F21" s="16">
         <v>0.1</v>
       </c>
-      <c r="G21" s="13">
-        <f t="shared" si="0"/>
-        <v>0.60000000000000009</v>
+      <c r="G21" s="16">
+        <f t="shared" si="0"/>
+        <v>0.70000000000000007</v>
       </c>
       <c r="H21" s="14"/>
-      <c r="I21" s="2" t="s">
-        <v>75</v>
+      <c r="I21" s="17" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1557,27 +1588,27 @@
         <v>20</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="D22" s="12">
         <v>3</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F22" s="13">
+        <v>149</v>
+      </c>
+      <c r="F22" s="16">
         <v>0.1</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="16">
         <f t="shared" si="0"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="H22" s="14"/>
-      <c r="I22" s="2" t="s">
-        <v>76</v>
+      <c r="I22" s="17" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1585,27 +1616,27 @@
         <v>21</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="D23" s="12">
         <v>3</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="F23" s="13">
+        <v>150</v>
+      </c>
+      <c r="F23" s="16">
         <v>0.1</v>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="16">
         <f t="shared" si="0"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="H23" s="14"/>
-      <c r="I23" s="2" t="s">
-        <v>77</v>
+      <c r="I23" s="17" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1613,27 +1644,27 @@
         <v>22</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="D24" s="12">
         <v>1</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="F24" s="13">
+        <v>151</v>
+      </c>
+      <c r="F24" s="16">
         <v>0.1</v>
       </c>
-      <c r="G24" s="13">
+      <c r="G24" s="16">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
       <c r="H24" s="14"/>
-      <c r="I24" s="2" t="s">
-        <v>77</v>
+      <c r="I24" s="17" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1641,55 +1672,53 @@
         <v>23</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="D25" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F25" s="13">
-        <v>0.32</v>
-      </c>
-      <c r="G25" s="13">
-        <f t="shared" si="0"/>
-        <v>0.32</v>
+        <v>152</v>
+      </c>
+      <c r="F25" s="16">
+        <v>0.23</v>
+      </c>
+      <c r="G25" s="16">
+        <f t="shared" si="0"/>
+        <v>0.46</v>
       </c>
       <c r="H25" s="14"/>
-      <c r="I25" s="2" t="s">
-        <v>78</v>
+      <c r="I25" s="17" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>24</v>
       </c>
-      <c r="B26" s="12" t="s">
-        <v>82</v>
+      <c r="B26" s="12">
+        <v>39012086</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="D26" s="12">
         <v>1</v>
       </c>
-      <c r="E26" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F26" s="13">
-        <v>0.23</v>
-      </c>
-      <c r="G26" s="13">
-        <f t="shared" si="0"/>
-        <v>0.23</v>
+      <c r="E26" s="12"/>
+      <c r="F26" s="16">
+        <v>0.66</v>
+      </c>
+      <c r="G26" s="16">
+        <f t="shared" si="0"/>
+        <v>0.66</v>
       </c>
       <c r="H26" s="14"/>
-      <c r="I26" s="2" t="s">
-        <v>81</v>
+      <c r="I26" s="17" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1697,27 +1726,25 @@
         <v>25</v>
       </c>
       <c r="B27" s="12">
-        <v>39012086</v>
+        <v>39012205</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="D27" s="12">
         <v>1</v>
       </c>
-      <c r="E27" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="F27" s="13">
-        <v>0.66</v>
-      </c>
-      <c r="G27" s="13">
-        <f t="shared" si="0"/>
-        <v>0.66</v>
+      <c r="E27" s="12"/>
+      <c r="F27" s="16">
+        <v>1.48</v>
+      </c>
+      <c r="G27" s="16">
+        <f t="shared" si="0"/>
+        <v>1.48</v>
       </c>
       <c r="H27" s="14"/>
-      <c r="I27" s="2" t="s">
-        <v>91</v>
+      <c r="I27" s="17" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1725,27 +1752,25 @@
         <v>26</v>
       </c>
       <c r="B28" s="12">
-        <v>39012205</v>
+        <v>39012206</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="D28" s="12">
         <v>1</v>
       </c>
-      <c r="E28" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="F28" s="13">
-        <v>1.48</v>
-      </c>
-      <c r="G28" s="13">
-        <f t="shared" si="0"/>
-        <v>1.48</v>
+      <c r="E28" s="12"/>
+      <c r="F28" s="16">
+        <v>1.2</v>
+      </c>
+      <c r="G28" s="16">
+        <f t="shared" si="0"/>
+        <v>1.2</v>
       </c>
       <c r="H28" s="14"/>
-      <c r="I28" s="2" t="s">
-        <v>95</v>
+      <c r="I28" s="17" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1753,27 +1778,25 @@
         <v>27</v>
       </c>
       <c r="B29" s="12">
-        <v>39012206</v>
+        <v>39000048</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D29" s="12">
-        <v>1</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="F29" s="13">
-        <v>1.2</v>
-      </c>
-      <c r="G29" s="13">
-        <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>18</v>
+      </c>
+      <c r="E29" s="12"/>
+      <c r="F29" s="16">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="G29" s="16">
+        <f t="shared" si="0"/>
+        <v>1.0979999999999999</v>
       </c>
       <c r="H29" s="14"/>
-      <c r="I29" s="2" t="s">
-        <v>98</v>
+      <c r="I29" s="17" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1781,27 +1804,25 @@
         <v>28</v>
       </c>
       <c r="B30" s="12">
-        <v>39000041</v>
+        <v>39000046</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D30" s="12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E30" s="12"/>
-      <c r="F30" s="13">
-        <v>0.15</v>
-      </c>
-      <c r="G30" s="13">
-        <f t="shared" si="0"/>
-        <v>1.5</v>
-      </c>
-      <c r="H30" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>101</v>
+      <c r="F30" s="16">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="G30" s="16">
+        <f t="shared" si="0"/>
+        <v>0.312</v>
+      </c>
+      <c r="H30" s="14"/>
+      <c r="I30" s="17" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1809,195 +1830,195 @@
         <v>29</v>
       </c>
       <c r="B31" s="12">
-        <v>39000039</v>
+        <v>430300007</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="D31" s="12">
         <v>6</v>
       </c>
       <c r="E31" s="12"/>
-      <c r="F31" s="13">
-        <v>0.16</v>
-      </c>
-      <c r="G31" s="13">
-        <f t="shared" si="0"/>
-        <v>0.96</v>
-      </c>
-      <c r="H31" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>104</v>
+      <c r="F31" s="16">
+        <v>0.18</v>
+      </c>
+      <c r="G31" s="16">
+        <f t="shared" si="0"/>
+        <v>1.08</v>
+      </c>
+      <c r="H31" s="14"/>
+      <c r="I31" s="17" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>30</v>
       </c>
-      <c r="B32" s="12">
-        <v>430300007</v>
+      <c r="B32" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="D32" s="12">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="E32" s="12"/>
-      <c r="F32" s="13">
-        <v>0.18</v>
-      </c>
-      <c r="G32" s="13">
-        <f t="shared" si="0"/>
-        <v>7.7399999999999993</v>
+      <c r="F32" s="16">
+        <v>0.48</v>
+      </c>
+      <c r="G32" s="16">
+        <f t="shared" si="0"/>
+        <v>0.48</v>
       </c>
       <c r="H32" s="14"/>
-      <c r="I32" s="2" t="s">
-        <v>105</v>
+      <c r="I32" s="17" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
         <v>31</v>
       </c>
-      <c r="B33" s="12">
-        <v>430252400</v>
+      <c r="B33" s="12" t="s">
+        <v>119</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D33" s="12">
         <v>1</v>
       </c>
-      <c r="E33" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="F33" s="13">
-        <v>1.34</v>
-      </c>
-      <c r="G33" s="13">
-        <f t="shared" si="0"/>
-        <v>1.34</v>
+      <c r="E33" s="12"/>
+      <c r="F33" s="16">
+        <v>1.07</v>
+      </c>
+      <c r="G33" s="16">
+        <f t="shared" si="0"/>
+        <v>1.07</v>
       </c>
       <c r="H33" s="14"/>
-      <c r="I33" s="2" t="s">
-        <v>107</v>
+      <c r="I33" s="17" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>32</v>
       </c>
-      <c r="B34" s="12">
-        <v>430251800</v>
+      <c r="B34" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="D34" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="F34" s="13">
-        <v>1.07</v>
-      </c>
-      <c r="G34" s="13">
-        <f t="shared" si="0"/>
-        <v>1.07</v>
-      </c>
-      <c r="H34" s="14"/>
-      <c r="I34" s="2" t="s">
-        <v>113</v>
+        <v>60</v>
+      </c>
+      <c r="F34" s="16">
+        <v>0.12</v>
+      </c>
+      <c r="G34" s="16">
+        <f t="shared" si="0"/>
+        <v>0.36</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="I34" s="17" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
         <v>33</v>
       </c>
-      <c r="B35" s="12">
-        <v>436450800</v>
+      <c r="B35" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="D35" s="12">
-        <v>1</v>
-      </c>
-      <c r="E35" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="F35" s="13">
-        <v>0.35</v>
-      </c>
-      <c r="G35" s="13">
-        <f t="shared" si="0"/>
-        <v>0.35</v>
-      </c>
-      <c r="H35" s="14"/>
-      <c r="I35" s="2" t="s">
-        <v>114</v>
+        <v>12</v>
+      </c>
+      <c r="E35" s="12"/>
+      <c r="F35" s="16">
+        <v>0.12</v>
+      </c>
+      <c r="G35" s="16">
+        <f t="shared" si="0"/>
+        <v>1.44</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="I35" s="17" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
         <v>34</v>
       </c>
-      <c r="B36" s="12" t="s">
-        <v>118</v>
+      <c r="B36" s="12">
+        <v>61900511621</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="D36" s="12">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="F36" s="13">
-        <v>0.12</v>
-      </c>
-      <c r="G36" s="13">
-        <f t="shared" si="0"/>
-        <v>0.36</v>
+        <v>68</v>
+      </c>
+      <c r="F36" s="16">
+        <v>0.17</v>
+      </c>
+      <c r="G36" s="16">
+        <f t="shared" si="0"/>
+        <v>1.53</v>
       </c>
       <c r="H36" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>119</v>
+        <v>61</v>
+      </c>
+      <c r="I36" s="17" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
         <v>35</v>
       </c>
-      <c r="B37" s="12" t="s">
-        <v>121</v>
+      <c r="B37" s="12">
+        <v>61900211621</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="D37" s="12">
-        <v>12</v>
-      </c>
-      <c r="E37" s="12"/>
-      <c r="F37" s="13">
-        <v>0.12</v>
-      </c>
-      <c r="G37" s="13">
-        <f t="shared" si="0"/>
-        <v>1.44</v>
+        <v>3</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F37" s="16">
+        <v>0.13</v>
+      </c>
+      <c r="G37" s="16">
+        <f t="shared" si="0"/>
+        <v>0.39</v>
       </c>
       <c r="H37" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>122</v>
+        <v>61</v>
+      </c>
+      <c r="I37" s="17" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2005,283 +2026,429 @@
         <v>36</v>
       </c>
       <c r="B38" s="12">
-        <v>61900511621</v>
+        <v>61900411621</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="D38" s="12">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="F38" s="13">
+        <v>76</v>
+      </c>
+      <c r="F38" s="16">
         <v>0.17</v>
       </c>
-      <c r="G38" s="13">
-        <f t="shared" si="0"/>
-        <v>1.53</v>
+      <c r="G38" s="16">
+        <f t="shared" si="0"/>
+        <v>0.17</v>
       </c>
       <c r="H38" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>125</v>
+        <v>61</v>
+      </c>
+      <c r="I38" s="17" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
         <v>37</v>
       </c>
-      <c r="B39" s="12">
-        <v>61900211621</v>
+      <c r="B39" s="12" t="s">
+        <v>77</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="D39" s="12">
-        <v>6</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="F39" s="13">
-        <v>0.13</v>
-      </c>
-      <c r="G39" s="13">
-        <f t="shared" si="0"/>
-        <v>0.78</v>
+        <v>28</v>
+      </c>
+      <c r="E39" s="12"/>
+      <c r="F39" s="16">
+        <v>0.15</v>
+      </c>
+      <c r="G39" s="16">
+        <f t="shared" si="0"/>
+        <v>4.2</v>
       </c>
       <c r="H39" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>129</v>
+        <v>61</v>
+      </c>
+      <c r="I39" s="17" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
         <v>38</v>
       </c>
-      <c r="B40" s="12">
-        <v>61900411621</v>
+      <c r="B40" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="D40" s="12">
-        <v>3</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="F40" s="13">
-        <v>0.17</v>
-      </c>
-      <c r="G40" s="13">
-        <f t="shared" si="0"/>
-        <v>0.51</v>
+        <v>2</v>
+      </c>
+      <c r="E40" s="12"/>
+      <c r="F40" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="G40" s="16">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="H40" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>130</v>
+        <v>158</v>
+      </c>
+      <c r="I40" s="17" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
         <v>39</v>
       </c>
-      <c r="B41" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="D41" s="12">
-        <v>32</v>
-      </c>
+      <c r="B41" s="15"/>
+      <c r="C41" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D41" s="15"/>
       <c r="E41" s="12"/>
-      <c r="F41" s="13">
-        <v>0.15</v>
-      </c>
+      <c r="F41" s="13"/>
       <c r="G41" s="13">
-        <f t="shared" si="0"/>
-        <v>4.8</v>
+        <f>D41*F41</f>
+        <v>0</v>
       </c>
       <c r="H41" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
         <v>40</v>
       </c>
-      <c r="B42" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D42" s="12">
-        <v>2</v>
-      </c>
-      <c r="E42" s="12"/>
-      <c r="F42" s="13">
+      <c r="B42" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4">
         <v>0.1</v>
       </c>
       <c r="G42" s="13">
-        <f t="shared" si="0"/>
-        <v>0.2</v>
-      </c>
-      <c r="H42" s="14" t="s">
-        <v>148</v>
+        <f t="shared" ref="G42:G56" si="1">D42*F42</f>
+        <v>0.1</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
         <v>41</v>
       </c>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="D43" s="12">
+      <c r="B43" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D43" s="1">
         <v>1</v>
       </c>
-      <c r="E43" s="12"/>
-      <c r="F43" s="13">
-        <v>4.99</v>
+      <c r="F43" s="4">
+        <v>0.1</v>
       </c>
       <c r="G43" s="13">
-        <f>D43*F43</f>
-        <v>4.99</v>
-      </c>
-      <c r="H43" s="14"/>
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
       <c r="I43" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
         <v>42</v>
       </c>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="D44" s="12">
+      <c r="B44" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D44" s="1">
         <v>1</v>
       </c>
-      <c r="E44" s="12"/>
-      <c r="F44" s="13">
-        <v>6.98</v>
+      <c r="F44" s="4">
+        <v>0.71</v>
       </c>
       <c r="G44" s="13">
-        <f>D44*F44</f>
-        <v>6.98</v>
-      </c>
-      <c r="H44" s="14" t="s">
-        <v>149</v>
+        <f t="shared" si="1"/>
+        <v>0.71</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
         <v>43</v>
       </c>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="13"/>
+      <c r="B45" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D45" s="1">
+        <v>1</v>
+      </c>
+      <c r="F45" s="4">
+        <v>0.43</v>
+      </c>
       <c r="G45" s="13">
-        <f>D45*F45</f>
+        <f t="shared" si="1"/>
+        <v>0.43</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="11">
+        <v>44</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D46" s="1">
+        <v>6</v>
+      </c>
+      <c r="F46" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="G46" s="13">
+        <f t="shared" si="1"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="11">
+        <v>45</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D47" s="1">
+        <v>3</v>
+      </c>
+      <c r="F47" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="G47" s="13">
+        <f t="shared" si="1"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="11">
+        <v>46</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D48" s="1">
+        <v>3</v>
+      </c>
+      <c r="F48" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="G48" s="13">
+        <f t="shared" si="1"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="11">
+        <v>47</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D49" s="1">
+        <v>6</v>
+      </c>
+      <c r="F49" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="G49" s="13">
+        <f t="shared" si="1"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="11">
+        <v>48</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D50" s="1">
+        <v>13.75</v>
+      </c>
+      <c r="F50" s="4">
+        <f>12.01/25</f>
+        <v>0.48039999999999999</v>
+      </c>
+      <c r="G50" s="13">
+        <f t="shared" si="1"/>
+        <v>6.6055000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="11">
+        <v>49</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D51" s="1">
+        <v>15.25</v>
+      </c>
+      <c r="F51" s="4">
+        <f>9.5/25</f>
+        <v>0.38</v>
+      </c>
+      <c r="G51" s="13">
+        <f t="shared" si="1"/>
+        <v>5.7949999999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="11">
+        <v>50</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D52" s="1">
+        <v>36.67</v>
+      </c>
+      <c r="F52" s="4">
+        <f>8.07/25</f>
+        <v>0.32280000000000003</v>
+      </c>
+      <c r="G52" s="13">
+        <f t="shared" si="1"/>
+        <v>11.837076000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="11">
+        <v>51</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D53" s="1">
+        <v>52</v>
+      </c>
+      <c r="F53" s="4">
+        <f>8.85/25</f>
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="G53" s="13">
+        <f t="shared" si="1"/>
+        <v>18.407999999999998</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="11">
+        <v>52</v>
+      </c>
+      <c r="B54" s="1">
+        <v>39012040</v>
+      </c>
+      <c r="D54" s="1">
+        <v>3</v>
+      </c>
+      <c r="F54" s="4">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G54" s="13">
+        <f t="shared" si="1"/>
+        <v>0.86999999999999988</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G55" s="13">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H45" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="12">
-        <v>44</v>
-      </c>
-      <c r="B46" s="12"/>
-      <c r="C46" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13">
-        <f>D46*F46</f>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G56" s="13">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H46" s="14" t="s">
-        <v>144</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I72" xr:uid="{5704B641-D666-4847-A317-F8C12FBC4158}"/>
+  <autoFilter ref="A2:I67" xr:uid="{5704B641-D666-4847-A317-F8C12FBC4158}"/>
   <hyperlinks>
     <hyperlink ref="I3" r:id="rId1" xr:uid="{27B6BC92-0FDD-4B4B-925B-C8616172702B}"/>
     <hyperlink ref="I4" r:id="rId2" xr:uid="{9CD98FD7-D968-48CB-B0EE-F8DE1956BEC5}"/>
-    <hyperlink ref="I5" r:id="rId3" xr:uid="{E651AC7D-7CE8-43AE-94E4-5CA2A7F255CD}"/>
-    <hyperlink ref="I8" r:id="rId4" xr:uid="{2945276B-C1D2-4FBE-96CB-44551DF27DC8}"/>
-    <hyperlink ref="I9" r:id="rId5" xr:uid="{A77656E5-953D-47FE-ADCB-E007813EB4E5}"/>
-    <hyperlink ref="I10" r:id="rId6" xr:uid="{77BBC6AF-CFD2-40D3-B45E-26BC978EC51F}"/>
-    <hyperlink ref="I11" r:id="rId7" xr:uid="{BF8D5FDE-40EE-4459-AD6E-86B427CC15A9}"/>
-    <hyperlink ref="I12" r:id="rId8" xr:uid="{3500D645-FE9C-4E31-A7BC-DFE4B455AFB0}"/>
-    <hyperlink ref="I13" r:id="rId9" xr:uid="{5715CC08-1A2D-461B-9484-CF055E9F324B}"/>
-    <hyperlink ref="I14" r:id="rId10" xr:uid="{0F2AA306-BD41-47B2-9F97-E46719DB4F1A}"/>
-    <hyperlink ref="I15" r:id="rId11" xr:uid="{8048AE8C-3072-49EE-B46A-5D8DA964C2AF}"/>
-    <hyperlink ref="I16" r:id="rId12" xr:uid="{036BF8F4-9CDA-4355-AAC0-FB3116414132}"/>
-    <hyperlink ref="I17" r:id="rId13" xr:uid="{09EA109D-AA2F-4F3B-8FBA-A217EF1A4D6C}"/>
-    <hyperlink ref="I18" r:id="rId14" xr:uid="{0C32AB6A-95E0-469F-A03C-7DFA8A740F54}"/>
-    <hyperlink ref="I19" r:id="rId15" xr:uid="{345DB927-057A-4B37-9198-113E75E9F5C9}"/>
-    <hyperlink ref="I20" r:id="rId16" xr:uid="{C0519B74-6030-48E1-AEA6-63900799EFE2}"/>
-    <hyperlink ref="I21" r:id="rId17" xr:uid="{46ABD8C6-B2E6-455A-80CB-A6FC2CF5887C}"/>
-    <hyperlink ref="I22" r:id="rId18" xr:uid="{7DCFBDB0-9092-4537-9761-431FCBC240FF}"/>
-    <hyperlink ref="I23" r:id="rId19" xr:uid="{4B9C3EFD-8C54-4B20-BE28-2F45279E83FC}"/>
-    <hyperlink ref="I24" r:id="rId20" xr:uid="{7E9BB57C-134B-4AF2-83CA-D1A8BF76C8B8}"/>
-    <hyperlink ref="I25" r:id="rId21" xr:uid="{1C9BB5EB-16A7-4390-9E57-340EE3871EFC}"/>
-    <hyperlink ref="I26" r:id="rId22" xr:uid="{AA0ADB72-F5F8-451F-B82A-6C22BC9B2237}"/>
-    <hyperlink ref="I27" r:id="rId23" xr:uid="{E2082D90-2464-4E5C-B3FC-F921E6FDD7D9}"/>
-    <hyperlink ref="I28" r:id="rId24" xr:uid="{798142E9-E020-4A80-9BBD-389FAE010D2E}"/>
-    <hyperlink ref="I29" r:id="rId25" xr:uid="{31824BC6-0EB0-4A53-9F55-AA4D586DE62A}"/>
-    <hyperlink ref="I30" r:id="rId26" xr:uid="{DCA6E157-428E-43C8-ACAE-E008734376D1}"/>
-    <hyperlink ref="I31" r:id="rId27" xr:uid="{F634B005-4425-43A9-8E6F-68310690DA88}"/>
-    <hyperlink ref="I32" r:id="rId28" xr:uid="{EDB0382D-6A51-428E-9948-72F64EC715A9}"/>
-    <hyperlink ref="I33" r:id="rId29" xr:uid="{7B675C9E-E4C4-4E4E-9787-7AA8CDC67EB5}"/>
-    <hyperlink ref="I34" r:id="rId30" xr:uid="{46AF37E1-55D5-4139-98A4-F5B154308127}"/>
-    <hyperlink ref="I35" r:id="rId31" xr:uid="{D13C01D4-23BB-4257-B360-62EB3D741A03}"/>
-    <hyperlink ref="I36" r:id="rId32" xr:uid="{C44B2E72-0CF3-4C81-BCA0-2F91ACAD5C48}"/>
-    <hyperlink ref="I37" r:id="rId33" xr:uid="{886D77AE-9801-4CFB-94E0-EF694AFB84AC}"/>
-    <hyperlink ref="I38" r:id="rId34" xr:uid="{FAC3FE17-0077-4C0F-8051-E38241BC89E7}"/>
-    <hyperlink ref="I39" r:id="rId35" xr:uid="{D0D3BAF3-0565-40F9-ABB4-F40473053C2C}"/>
-    <hyperlink ref="I40" r:id="rId36" xr:uid="{13E395D8-DF28-4EEE-ADE8-B308AC979A6B}"/>
-    <hyperlink ref="I41" r:id="rId37" xr:uid="{A11EE872-4FB7-4BAB-BFF9-F03BB5ACCC6A}"/>
-    <hyperlink ref="I43" r:id="rId38" xr:uid="{980B216C-BA1C-4B61-B176-B13CF2690539}"/>
-    <hyperlink ref="I44" r:id="rId39" xr:uid="{D4EA5E7B-9A25-42E6-A746-9E14D46A80DD}"/>
-    <hyperlink ref="I45" r:id="rId40" xr:uid="{82B6D0E9-2B4A-413B-A0F4-FFBC23D29C22}"/>
-    <hyperlink ref="I42" r:id="rId41" xr:uid="{668765E4-8FB3-430B-AAD3-996ED8786F98}"/>
-    <hyperlink ref="I7" r:id="rId42" xr:uid="{376CD8A6-58A6-4535-BFDB-73F13C420A17}"/>
+    <hyperlink ref="I14" r:id="rId3" xr:uid="{0F2AA306-BD41-47B2-9F97-E46719DB4F1A}"/>
+    <hyperlink ref="I15" r:id="rId4" xr:uid="{8048AE8C-3072-49EE-B46A-5D8DA964C2AF}"/>
+    <hyperlink ref="I16" r:id="rId5" xr:uid="{036BF8F4-9CDA-4355-AAC0-FB3116414132}"/>
+    <hyperlink ref="I18" r:id="rId6" xr:uid="{0C32AB6A-95E0-469F-A03C-7DFA8A740F54}"/>
+    <hyperlink ref="I19" r:id="rId7" xr:uid="{345DB927-057A-4B37-9198-113E75E9F5C9}"/>
+    <hyperlink ref="I20" r:id="rId8" xr:uid="{C0519B74-6030-48E1-AEA6-63900799EFE2}"/>
+    <hyperlink ref="I21" r:id="rId9" xr:uid="{46ABD8C6-B2E6-455A-80CB-A6FC2CF5887C}"/>
+    <hyperlink ref="I22" r:id="rId10" xr:uid="{7DCFBDB0-9092-4537-9761-431FCBC240FF}"/>
+    <hyperlink ref="I23" r:id="rId11" xr:uid="{4B9C3EFD-8C54-4B20-BE28-2F45279E83FC}"/>
+    <hyperlink ref="I24" r:id="rId12" xr:uid="{7E9BB57C-134B-4AF2-83CA-D1A8BF76C8B8}"/>
+    <hyperlink ref="I25" r:id="rId13" xr:uid="{AA0ADB72-F5F8-451F-B82A-6C22BC9B2237}"/>
+    <hyperlink ref="I26" r:id="rId14" xr:uid="{E2082D90-2464-4E5C-B3FC-F921E6FDD7D9}"/>
+    <hyperlink ref="I27" r:id="rId15" xr:uid="{798142E9-E020-4A80-9BBD-389FAE010D2E}"/>
+    <hyperlink ref="I28" r:id="rId16" xr:uid="{31824BC6-0EB0-4A53-9F55-AA4D586DE62A}"/>
+    <hyperlink ref="I31" r:id="rId17" xr:uid="{EDB0382D-6A51-428E-9948-72F64EC715A9}"/>
+    <hyperlink ref="I33" r:id="rId18" xr:uid="{46AF37E1-55D5-4139-98A4-F5B154308127}"/>
+    <hyperlink ref="I34" r:id="rId19" xr:uid="{C44B2E72-0CF3-4C81-BCA0-2F91ACAD5C48}"/>
+    <hyperlink ref="I35" r:id="rId20" xr:uid="{886D77AE-9801-4CFB-94E0-EF694AFB84AC}"/>
+    <hyperlink ref="I36" r:id="rId21" xr:uid="{FAC3FE17-0077-4C0F-8051-E38241BC89E7}"/>
+    <hyperlink ref="I37" r:id="rId22" xr:uid="{D0D3BAF3-0565-40F9-ABB4-F40473053C2C}"/>
+    <hyperlink ref="I38" r:id="rId23" xr:uid="{13E395D8-DF28-4EEE-ADE8-B308AC979A6B}"/>
+    <hyperlink ref="I39" r:id="rId24" xr:uid="{A11EE872-4FB7-4BAB-BFF9-F03BB5ACCC6A}"/>
+    <hyperlink ref="I40" r:id="rId25" xr:uid="{668765E4-8FB3-430B-AAD3-996ED8786F98}"/>
+    <hyperlink ref="I7" r:id="rId26" xr:uid="{376CD8A6-58A6-4535-BFDB-73F13C420A17}"/>
+    <hyperlink ref="I29" r:id="rId27" xr:uid="{272156EC-7A7C-4D25-AF5F-31AB665C274A}"/>
+    <hyperlink ref="I42" r:id="rId28" xr:uid="{243FE14C-88C0-49E7-AA5A-273977975A9A}"/>
+    <hyperlink ref="I43" r:id="rId29" xr:uid="{FC61CAEB-C864-45E8-8231-37308972695D}"/>
+    <hyperlink ref="I44" r:id="rId30" xr:uid="{3B20D85E-9DF5-433F-8EF9-E52E4976EE5D}"/>
+    <hyperlink ref="I45" r:id="rId31" xr:uid="{0DA86E7D-1154-48E4-A55E-301A050D0053}"/>
+    <hyperlink ref="I49" r:id="rId32" xr:uid="{F131D3B1-28D0-4DF5-BE08-695EC701C1F9}"/>
+    <hyperlink ref="I48" r:id="rId33" xr:uid="{6C1509B0-8A5A-4CE9-8B96-2CBFD573283A}"/>
+    <hyperlink ref="I46" r:id="rId34" xr:uid="{2E848825-B848-48B7-879C-F71CBB062145}"/>
+    <hyperlink ref="I47" r:id="rId35" xr:uid="{693CAE50-24E8-4FE9-855A-E19E9185B4B4}"/>
+    <hyperlink ref="I30" r:id="rId36" xr:uid="{83CAD37A-9CF8-4144-8001-3DD3954A362B}"/>
+    <hyperlink ref="I54" r:id="rId37" xr:uid="{D5BBF9DB-D9C0-4CC9-90CF-A42790BBE595}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/DuePrint3 BOM.xlsx
+++ b/DuePrint3 BOM.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A7C2F95-A385-47A1-A6DD-365DEDA3304F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="1860" windowWidth="35895" windowHeight="17805" xr2:uid="{EE4BCC0D-CA0F-44AB-9A6C-651FC0043629}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25800" windowHeight="21000" xr2:uid="{EE4BCC0D-CA0F-44AB-9A6C-651FC0043629}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
